--- a/신고신저가_20260807.xlsx
+++ b/신고신저가_20260807.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,56 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 지수는 눌렸는데 신고가 99 대 신저가 18 — 실적 서프라이즈가 개별 종목을 끌어올린 종목장. 금융 신고가 27종 vs 유틸·파이프라인 신저가 6종 조합은 금리 되밀림 국면 성격으로 추정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/6): 다우 -0.85%·S&amp;P -0.18%·나스닥 -0.06%, 신고 99(NEW 43)/신저 18(NEW 9). 금융 순강도 +27(12MF PER 15.3, 표본 162)·헬스테크 +10 강세, 유틸 -2(XLU 1D -0.6%·1M -4.4%)·산업서비스 -1 약세. 실적 서프라이즈 급등(인스메드 +33.9%, 페이컴 +23.6%, CACI +21.4%, 챠임 +20.6%) vs 가이던스 실망 급락(앱러빈 -19.7%, 웨스턴디지털 -13.0%). 신저가에 유틸 3종(PPL·얼라이언트·셈프라)·파이프라인 3종(DT미드스트림·엔브리지·TC에너지) 집중.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/6): 신고 12(NEW 10) 전원 4-6월 결산 서프라이즈 — 카오 +12.8%(이익 상향+주주우대 신설), 반다이남코 +10.9%(완구 세그먼트이익 88.8%↑), 도레이 +9.3%(순이익 82%↑). 섹터ETF는 의약품 +2.6%·식품 +2.4%·자동차 +2.4% 강세, 철강·비철 -4.0%(주간 +13.9%에서 반락)·전기정밀 -1.9% 약세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/6): 항셍 -1.49%·항셍테크 -2.28% 하락에도 신고 6. 워프REIC +13.7%(1H26 배당성향 65%→90% 상향, 중간배당 42%↑)가 부동산 리레이팅 트리거. 중지쉬촹(AI 광모듈) +3.1% 신고가로 AI 하드웨어 온기 잔존.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/6): 상해 +0.57%·CSI300 -0.15%. 신고 5 중 3종이 금·비철(쯔진광업·츠펑황금·시부광업) — 국제 금값 온스 4300달러 돌파 랠리가 관통. 나머지는 헝리중공업(구 송파도자기, 조선 재편) +4.1%. 유색금속 ETF +0.7%·반도체 +1.4% vs 의약 -2.1%·신에너지차 -1.4%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①금융 신고 27 vs 채권프록시 신저 = 금리 되밀림 지속 여부 ②AI 하드웨어 균열(웨스턴디지털·앱러빈 급락 vs 중지쉬촹 신고가) 확산 여부 ③금 4300달러 랠리 유지 시 중화권 광산주 추가 신고가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 美는 한국시간 8/7 새벽 마감분, 日·홍콩·中은 8/6 마감 확정치. 신저가 1위 하니웰에어로스페이스(-23.2%)는 스핀오프 신규상장이라 52주 저가 기준 기간이 짧아 해석 주의.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +763,19 @@
       <c r="C2" t="n">
         <v>7709.96</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.18</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="5" t="n">
         <v>3.66</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.04</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>4.68</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>12.63</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +801,19 @@
       <c r="C3" t="n">
         <v>26348.35</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.06</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="5" t="n">
         <v>4.88</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.85</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="5" t="n">
         <v>1.97</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>13.37</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +839,19 @@
       <c r="C4" t="n">
         <v>6598.26</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>3.76</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>16.51</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="4" t="n">
         <v>-18.05</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-4.88</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>56.57</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +877,19 @@
       <c r="C5" t="n">
         <v>66300.44</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="5" t="n">
         <v>3.66</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="5" t="n">
         <v>7.92</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>-4.93</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>5.52</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>31.71</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +915,19 @@
       <c r="C6" t="n">
         <v>3900.35</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.57</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="5" t="n">
         <v>2.51</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="4" t="n">
         <v>-1.78</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-6.69</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.73</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +953,19 @@
       <c r="C7" t="n">
         <v>4651.31</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>-0.15</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="5" t="n">
         <v>2.23</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>-2.19</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="5" t="n">
         <v>0.46</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +991,19 @@
       <c r="C8" t="n">
         <v>25530.28</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>-1.49</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>5.5</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-2.61</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.39</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1029,19 @@
       <c r="C9" t="n">
         <v>4820.78</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-2.28</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-2.99</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-12.6</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1160,7 @@
       <c r="F2" t="n">
         <v>27</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1201,7 @@
       <c r="F3" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1242,7 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1283,7 @@
       <c r="F5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1324,7 @@
       <c r="F6" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1365,7 @@
       <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1406,7 @@
       <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1447,7 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1488,7 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1529,7 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1570,7 @@
       <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1611,7 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1652,7 @@
       <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1639,7 +1693,7 @@
       <c r="F15" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1680,7 +1734,7 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1721,7 +1775,7 @@
       <c r="F17" t="n">
         <v>-1</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1762,7 +1816,7 @@
       <c r="F18" t="n">
         <v>-1</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1801,7 +1855,7 @@
       <c r="F19" t="n">
         <v>-2</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +1978,7 @@
       <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1965,7 +2019,7 @@
       <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2006,7 +2060,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2045,7 +2099,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2086,7 +2140,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2127,7 +2181,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2166,7 +2220,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2207,7 +2261,7 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2246,7 +2300,7 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2285,7 +2339,7 @@
       <c r="F31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2638,7 +2692,7 @@
       <c r="F40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2679,7 +2733,7 @@
       <c r="F41" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2720,7 +2774,7 @@
       <c r="F42" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2761,7 +2815,7 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2802,7 +2856,7 @@
       <c r="F44" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2843,7 +2897,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3360,7 +3414,7 @@
       <c r="F58" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G58" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3399,7 +3453,7 @@
       <c r="F59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3438,7 +3492,7 @@
       <c r="F60" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -4064,30 +4118,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4108,90 +4163,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4213,58 +4273,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.3%지만 주간 +5.5%로 상위권 유지. 테크서비스 순강도 +7(MSFT 신고가), 반면 웨스턴디지털·앱러빈 급락으로 내부 균열</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>9.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4284,58 +4349,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.2%·3M +13.6%로 3개월 최상위. 헬스테크 순강도 +10, 인스메드 +33.9%·프락시스 +16.0% 신약 모멘텀</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>13.6</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>7.1</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4355,58 +4425,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.3%지만 신고가 27종으로 전 섹터 최다(순강도 +27). 12MF PER 15.3(표본 162)로 밸류 부담 낮음, 금리 되밀림 수혜 추정</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>5.2</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4426,58 +4501,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.5%·주간 +5.1%. 경기소비재 순강도 +6이나 3M -1.3%로 중기 흐름은 여전히 부진</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4497,58 +4577,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.3%로 당일 상위. 다만 순강도 +1(밀리콤 +13.6% 정도)이고 3M -5.0%로 섹터 중 최약</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>4.3</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4568,58 +4653,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.9%로 당일 최하위권. 산업서비스 순강도 -1(엔브리지·TC에너지 신저), 프로듀서 +5와 혼재</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4639,58 +4729,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.3%·주간 -0.4%. 순강도 +2로 방어적, 특별한 촉매 없이 지수 등락에 연동 추정</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4710,58 +4805,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.5%로 전 섹터 최강. 다만 에너지광물 신고·신저 모두 0, 12MF PER 10.1로 최저 밸류</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4781,58 +4881,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.6%·1M -4.4%로 최약. 순강도 -2, PPL·얼라이언트·셈프라 신저가 — 금리 되밀림 직격 추정</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4852,58 +4957,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.9%지만 1M +4.0%. 비에너지광물 순강도 +2로 금속 랠리 온기 일부 반영</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4923,58 +5033,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.9%·주간 -1.1%. 아메리칸홈4렌트·인비테이션홈스는 신고가지만 12MF PER 40배대로 부담</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4994,58 +5109,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5065,58 +5181,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>9</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5136,58 +5253,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-7.8</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>8.9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5207,58 +5325,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5278,58 +5397,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5349,58 +5469,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5420,58 +5541,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-17.6</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>43.4</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5491,58 +5613,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-5.8</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>6</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5562,58 +5685,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5633,58 +5757,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5704,58 +5829,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>15</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5775,58 +5901,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>13</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5846,58 +5973,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5917,58 +6045,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5988,58 +6117,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>46</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6059,58 +6189,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6130,58 +6261,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-5.7</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6201,58 +6333,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>5.4</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6272,58 +6405,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>-2.7</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>5.5</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6343,56 +6477,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6410,58 +6545,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.4%·주간 +9.3%로 반등 지속. 다만 1M -21.8%로 낙폭 회복 초기 국면</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-21.8</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6481,58 +6621,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.2%·주간 +10.3%. 1M -14.4% 조정 후 반등, AI 테마 재유입 추정</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-14.4</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6552,58 +6697,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>1D +1.2%·주간 +15.1%로 주간 최강. 홍콩 중지쉬촹 신고가와 같은 AI 광통신 온기</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>15.1</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-14.8</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>33.6</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6623,56 +6773,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.4%·3M -23.1%로 중기 최약. 신에너지차 신고가 종목 없음</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>-4.7</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-23.1</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-12.4</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6690,58 +6845,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.1%·3M -23.0%. 방산 신고가 부재, 주간 +5.8% 반등에 그침</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>-6.9</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-17.3</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6761,56 +6921,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.2%·3M -22.9%. 태양광 신고가 부재, 공급과잉 국면 지속 추정</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>-6</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-22.9</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6828,58 +6993,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.7%·주간 -4.0%지만 1M +11.3%. 백주 반등 후 단기 숨고르기</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-19</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>12</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6899,58 +7069,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.5%·주간 -4.2%. 은행은 3M +2.5%로 방어적, 신고가 종목은 없음</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>6</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6970,58 +7145,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>1D +0.7%·주간 +9.7%·1M +9.5%. 금값 4300달러 랠리로 쯔진광업·츠펑황금 신고가</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>9.5</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-13.1</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7041,58 +7221,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>1D 0.0%·1M +2.5%. 부동산 신고가 부재, 3M -18.9%로 중기 약세 지속</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-18.9</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-19.5</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>13</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7112,58 +7297,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>1D -1.2%·주간 -0.9%. 증권 신고가 부재, 거래대금 모멘텀 둔화 추정</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-9.5</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7183,58 +7373,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>1D -2.1%로 당일 최약. 베이원메디신 상반기 서프라이즈에도 -4.1% 차익실현, 1M +8.6% 되돌림</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7254,58 +7449,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>1D -0.7%·주간 -4.3%지만 1M +7.0%. 소비 신고가 부재, 반등 후 조정 국면</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-8.9</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-15.6</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7317,7 +7517,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-4"/>
@@ -7329,7 +7529,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-5.3"/>
@@ -7341,7 +7541,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-21.8"/>
@@ -7353,7 +7553,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-23.1"/>
@@ -7365,7 +7565,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-19.5"/>
@@ -7377,7 +7577,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7389,7 +7589,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7401,7 +7601,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7413,7 +7613,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7425,7 +7625,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7437,7 +7637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7551,12 +7751,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7600,15 +7800,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7656,15 +7856,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7712,10 +7912,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7768,10 +7968,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7824,10 +8024,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7880,15 +8080,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7932,10 +8132,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7988,10 +8188,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8042,10 +8242,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8098,14 +8298,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) 이튼(전력관리·전기장비): Q2 EPS·매출 상회, 전력인프라 수주 급증·FY26 가이던스 상향, 에버코어 목표가 상향</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8152,15 +8352,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8202,10 +8402,10 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8258,15 +8458,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8314,10 +8514,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8366,19 +8566,19 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>(전일) 엔브리지(캐나다 에너지 파이프라인): 개별 뉴스 없음, 에너지 섹터 약세(추정)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8426,15 +8626,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8476,15 +8676,15 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8532,15 +8732,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8588,15 +8788,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8640,10 +8840,10 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8692,10 +8892,10 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8744,15 +8944,15 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8796,15 +8996,15 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8846,10 +9046,10 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8902,15 +9102,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8958,15 +9158,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9014,10 +9214,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9066,15 +9266,15 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9122,10 +9322,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9174,10 +9374,10 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9230,15 +9430,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9284,10 +9484,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9336,15 +9536,15 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9388,10 +9588,10 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9444,15 +9644,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9496,15 +9696,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9548,10 +9748,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9604,10 +9804,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9656,10 +9856,10 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9708,10 +9908,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9764,10 +9964,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9816,10 +10016,10 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9872,10 +10072,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9924,14 +10124,14 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr">
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>(전일) 인거솔랜드(산업용 압축기·펌프): Q2 실적·가이던스 상향, Baird 목표가 상향에 신고가</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9984,10 +10184,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr"/>
+      <c r="N46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10036,15 +10236,15 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10088,10 +10288,10 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10144,14 +10344,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="8" t="inlineStr">
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>(전일) 테레다인(계측·이미징 장비): 신규 촉매 미확인, 실적 호조 후 고점 유지</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10204,10 +10404,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10256,15 +10456,15 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10304,10 +10504,10 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10358,14 +10558,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N53" s="8" t="inlineStr">
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>(전일) 벤딩스푼스(앱 인수·운영 이탈리아 테크): +16.8% 급등, 촉매 미확인(상장 초기 변동성 추정)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10414,15 +10614,15 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10466,15 +10666,15 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10522,10 +10722,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10578,14 +10778,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="8" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>(전일) 샤크닌자(소형가전): 2분기 서프라이즈·연간 가이던스 상향으로 +8.3%</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10638,15 +10838,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="8" t="inlineStr"/>
+      <c r="N58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10686,10 +10886,10 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10738,10 +10938,10 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" s="8" t="inlineStr"/>
+      <c r="N60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10792,19 +10992,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="8" t="inlineStr">
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>(전일) 아르시스(방산·항공우주 부품): 2분기 매출 25%↑·EBITDA 38%↑, 연간 가이던스 상향</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10852,15 +11052,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10908,15 +11108,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="8" t="inlineStr"/>
+      <c r="N63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10958,10 +11158,10 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11014,15 +11214,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11066,10 +11266,10 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11122,15 +11322,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11178,15 +11378,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11232,10 +11432,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11284,10 +11484,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11340,10 +11540,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11392,15 +11592,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11444,10 +11644,10 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11494,10 +11694,10 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11544,19 +11744,19 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr">
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>(전일) 유니티소프트웨어(게임엔진·3D툴): Q2 실적(8/5) 기대·전략매출 35% 성장 확인, 7/31 급락분 반등에 나스닥 강세 수혜</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11604,15 +11804,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11660,10 +11860,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11716,14 +11916,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="8" t="inlineStr">
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>(전일) RB글로벌(산업장비 경매 마켓플레이스): 실적 실망으로 -13.9%, 신저가</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11776,10 +11976,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11830,15 +12030,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11882,10 +12082,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11932,10 +12132,10 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11984,15 +12184,15 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="7" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12040,10 +12240,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12096,15 +12296,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12152,10 +12352,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12204,10 +12404,10 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12256,10 +12456,10 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12308,10 +12508,10 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12362,15 +12562,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12418,10 +12618,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
+      <c r="A92" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12470,10 +12670,10 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12522,10 +12722,10 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12570,10 +12770,10 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12624,15 +12824,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N95" s="8" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B96" s="7" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12674,15 +12874,15 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12726,10 +12926,10 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12782,10 +12982,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N98" s="8" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12838,15 +13038,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12892,10 +13092,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="8" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12948,15 +13148,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N101" s="8" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13000,10 +13200,10 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13050,10 +13250,10 @@
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" s="8" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13104,14 +13304,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N104" s="8" t="inlineStr">
+      <c r="N104" s="10" t="inlineStr">
         <is>
           <t>(전일) 찰스리버랩스(신약 전임상 CRO): 2분기 서프라이즈·가이던스 상향, 바이오텍 수요 회복</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="inlineStr">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13162,10 +13362,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N105" s="8" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13218,15 +13418,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="8" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13268,15 +13468,15 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="7" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13320,15 +13520,15 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" s="8" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13372,15 +13572,15 @@
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" s="8" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13424,15 +13624,15 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13478,10 +13678,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="8" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13528,14 +13728,14 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="8" t="inlineStr">
+      <c r="N112" s="10" t="inlineStr">
         <is>
           <t>(전일) 다비타(신장투석 체인): 2분기 EPS 상회에도 가이던스 우려로 -17%, 신저가</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13584,19 +13784,19 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" s="8" t="inlineStr">
+      <c r="N113" s="10" t="inlineStr">
         <is>
           <t>(전일) 드래프트킹스(온라인 스포츠베팅): 플러터 실적 쇼크 여파로 동반 -7.8%</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13640,15 +13840,15 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13692,15 +13892,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N115" s="8" t="inlineStr"/>
+      <c r="N115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13744,15 +13944,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N116" s="8" t="inlineStr"/>
+      <c r="N116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13800,15 +14000,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N117" s="8" t="inlineStr"/>
+      <c r="N117" s="10" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13854,7 +14054,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N118" s="8" t="inlineStr"/>
+      <c r="N118" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N118"/>
@@ -13960,12 +14160,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14007,10 +14207,10 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14063,19 +14263,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 키엔스(FA 센서·측정기기): 엔저에 기계·반도체 반등, 신고가 랠리 연장</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14121,10 +14321,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14173,19 +14373,19 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 일본제철(고로 철강): 1분기 실적 상향수정으로 +4%, 철강·비철 섹터 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14231,15 +14431,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14283,15 +14483,15 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14333,15 +14533,15 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14385,15 +14585,15 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14433,15 +14633,15 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14485,15 +14685,15 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14541,15 +14741,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14593,7 +14793,7 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N13"/>
@@ -14699,12 +14899,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14752,10 +14952,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14808,14 +15008,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) 촹커실업(밀워키·라이오비 전동공구): 상반기 순이익 +17.5%·배당 20%↑·5억달러 자사주로 +8.1%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14864,14 +15064,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) 야오밍바이오(바이오의약 CDMO): 야오밍캉더 실적발 위탁개발 업종 훈풍에 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14922,19 +15122,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 캐세이퍼시픽(홍콩 국적 항공사): 상반기 순이익 65~75% 급증 전망 공시로 강세</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14976,15 +15176,15 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15028,7 +15228,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
@@ -15134,12 +15334,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15183,15 +15383,15 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15235,15 +15435,15 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15289,10 +15489,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15343,19 +15543,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) 시부쾅예(구리·아연·몰리브덴 광산): 상반기 순이익 +123% 사상 최고, 유색금속 강세로 +7.4%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15397,7 +15597,7 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N6"/>

--- a/신고신저가_20260807.xlsx
+++ b/신고신저가_20260807.xlsx
@@ -8402,7 +8402,11 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>웨스턴디지털(HDD·데이터 스토리지): 실적 서프라이즈에도 가이던스 미흡+밸류 부담</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -8626,7 +8630,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="10" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>앱러빈(모바일 광고테크): 2분기 매출 컨센 하회+3분기 가이던스 부진</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9102,7 +9110,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="10" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>모토로라솔루션즈(공공안전 통신장비): 2분기 서프라이즈+LMR 수요로 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -9696,7 +9708,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N37" s="10" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr">
+        <is>
+          <t>하니웰에어로스페이스(항공우주 부품, 스핀오프 신규상장): 특별한 뉴스 없음(상장 초기 수급·밸류 조정 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -10404,7 +10420,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N50" s="10" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr">
+        <is>
+          <t>ATI(항공우주 특수금속소재): 2분기 매출·EPS 서프라이즈, 항공 수요 강세</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -10504,7 +10524,11 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="10" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr">
+        <is>
+          <t>인스메드(희귀 폐질환 신약): TPIP 12개월 데이터 호조+BMO 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -10886,7 +10910,11 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="10" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr">
+        <is>
+          <t>텍사스퍼시픽랜드(퍼미안 분지 토지·로열티): 2분기 실적 후 로열티 성장 둔화 우려</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -11158,7 +11186,11 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="10" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>페어아이작(FICO 신용점수): VantageScore 경쟁 심화+실적 우려로 약세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -11746,7 +11778,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" s="10" t="inlineStr">
         <is>
-          <t>(전일) 유니티소프트웨어(게임엔진·3D툴): Q2 실적(8/5) 기대·전략매출 35% 성장 확인, 7/31 급락분 반등에 나스닥 강세 수혜</t>
+          <t>유니티소프트웨어(게임엔진): 2분기 매출 24% 증가 서프라이즈+3분기 가이던스 상회</t>
         </is>
       </c>
     </row>
@@ -11918,7 +11950,7 @@
       </c>
       <c r="N78" s="10" t="inlineStr">
         <is>
-          <t>(전일) RB글로벌(산업장비 경매 마켓플레이스): 실적 실망으로 -13.9%, 신저가</t>
+          <t>RB글로벌(중고 장비 경매 마켓플레이스): 8/4 실적 후 테이크레이트 우려 지속</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12906,11 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="10" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr">
+        <is>
+          <t>CACI인터내셔널(국방IT 컨설팅): 4분기 EPS 컨센 큰폭 상회+가이던스 개선</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -13678,7 +13714,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N111" s="10" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr">
+        <is>
+          <t>챠임파이낸셜(모바일 챌린저뱅크): 2분기 GAAP 흑자전환+매출 가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -13840,7 +13880,11 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="10" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr">
+        <is>
+          <t>페이컴소프트웨어(인사·급여 SaaS): 2분기 실적 서프라이즈+가이던스 상향</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
@@ -13892,7 +13936,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N115" s="10" t="inlineStr"/>
+      <c r="N115" s="10" t="inlineStr">
+        <is>
+          <t>프락시스정밀의학(중추신경계 신약): FDA 중간검토 통과(자문위 불필요)+손실 축소</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -14431,7 +14479,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>카오(생활용품·화장품): 4-6월 영업이익 서프라이즈, 26년12월기 이익 상향+주주우대 신설</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -14483,7 +14535,11 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>니혼페인트(도료): 8/7 실적발표 앞두고 SMBC닛코 목표가 상향 등 기대감에 4일 연속 상승</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -14533,7 +14589,11 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>반다이남코(완구·게임): 1분기 완구 세그먼트이익 88.8% 증가, 실적·배당 상향+자사주매입</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -14685,7 +14745,11 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr"/>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>도레이(합섬·탄소섬유 소재): 1분기 순이익 82% 급증(보잉향 탄소섬유·차량용 수지), 상반기 전망 상향</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14741,7 +14805,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N12" s="10" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>야마하발동기(오토바이·마린 엔진): 8/4 중간결산 영업이익 88.6% 증가+실적 상향, 상장 후 최고가</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14952,7 +15020,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>중지쉬촹(AI데이터센터용 광모듈·광트랜시버): 특별한 뉴스 없음(AI연산 광통신 섹터 강세 추정)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -15176,7 +15248,11 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>차이나골드인터내셔널(금·구리 광산): 특별한 뉴스 없음(금값 랠리 속 보합권 수급)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -15228,7 +15304,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>워프REIC(홍콩 하버시티 등 상업부동산): 1H26 배당성향 65%→90% 상향, 중간배당 42% 증가(주당 0.94홍콩달러)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N7"/>
@@ -15383,7 +15463,11 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>쯔진광업(금·구리 채굴 대형사): 국제 금값 온스당 4300달러 돌파 랠리에 동반 상승</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -15435,7 +15519,11 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>베이원메디신(구 베이진, 신약개발 바이오): 상반기 서프라이즈에도 파이프라인 우려로 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -15489,7 +15577,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>헝리중공업(구 송파도자기, 조선사로 자산 재편): 상반기 순이익 456% 급증 전망+조선업 호조</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -15545,7 +15637,7 @@
       </c>
       <c r="N5" s="10" t="inlineStr">
         <is>
-          <t>(전일) 시부쾅예(구리·아연·몰리브덴 광산): 상반기 순이익 +123% 사상 최고, 유색금속 강세로 +7.4%</t>
+          <t>시부광업(구리·납·아연 채굴제련): 특별한 촉매 없음(금속가 랠리 후 차익실현 조정 추정)</t>
         </is>
       </c>
     </row>
@@ -15597,7 +15689,11 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>츠펑황금(금광 채굴): 국제 금값 4300달러 돌파 랠리에 동반 상승</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N6"/>
